--- a/apps/cards/resources/card_templates/shrm5.xlsx
+++ b/apps/cards/resources/card_templates/shrm5.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ШРМ 5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ШРМ 5" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ШРМ 5'!$A$1:$P$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ШРМ 5'!$A$1:$R$43</definedName>
   </definedNames>
   <calcPr calcId="162913" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
@@ -546,7 +546,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>12</col>
@@ -566,22 +566,22 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="7715250" y="1257301"/>
           <a:ext cx="1828799" cy="1362074"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -857,7 +857,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:T43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -865,12 +865,6 @@
     <col width="8" customWidth="1" style="20" min="1" max="5"/>
     <col width="9" customWidth="1" style="20" min="6" max="6"/>
     <col width="8" customWidth="1" style="20" min="7" max="18"/>
-    <col width="13" customWidth="1" style="20" min="10" max="10"/>
-    <col width="13" customWidth="1" style="20" min="11" max="11"/>
-    <col width="13" customWidth="1" style="20" min="12" max="12"/>
-    <col width="13" customWidth="1" style="20" min="13" max="13"/>
-    <col width="13" customWidth="1" style="20" min="14" max="14"/>
-    <col width="13" customWidth="1" style="20" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="20">
@@ -1027,30 +1021,19 @@
       <c r="D13" s="75" t="n"/>
       <c r="E13" s="76" t="n"/>
       <c r="F13" s="35" t="n"/>
-      <c r="G13" s="22" t="n"/>
-      <c r="K13" s="64" t="inlineStr">
+    </row>
+    <row r="14" ht="27.75" customHeight="1" s="20">
+      <c r="G14" s="22" t="n"/>
+      <c r="K14" s="64" t="inlineStr">
         <is>
           <t>Уважаемый пациент!</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="27.75" customHeight="1" s="20">
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Перед выпиской сдайте «Индивидуальную </t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="16" t="n"/>
-      <c r="N14" s="16" t="n"/>
-      <c r="O14" s="16" t="n"/>
-      <c r="P14" s="16" t="n"/>
-    </row>
     <row r="15" ht="24.75" customHeight="1" s="20">
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>программу» на пост медицинской сестре.</t>
+          <t xml:space="preserve">Перед выпиской сдайте «Индивидуальную </t>
         </is>
       </c>
       <c r="K15" s="16" t="n"/>
@@ -1061,13 +1044,17 @@
       <c r="P15" s="16" t="n"/>
     </row>
     <row r="16" ht="24.75" customHeight="1" s="20">
-      <c r="J16" s="49" t="n"/>
-      <c r="K16" s="49" t="n"/>
-      <c r="L16" s="49" t="n"/>
-      <c r="M16" s="49" t="n"/>
-      <c r="N16" s="49" t="n"/>
-      <c r="O16" s="49" t="n"/>
-      <c r="P16" s="49" t="n"/>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>программу» на пост медицинской сестре.</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
     </row>
     <row r="17" ht="1.5" customHeight="1" s="20">
       <c r="J17" s="49" t="n"/>
@@ -1496,6 +1483,7 @@
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="A37:B37"/>
+    <mergeCell ref="K14:P14"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="C7:E7"/>
@@ -1503,7 +1491,6 @@
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="A33:B33"/>
-    <mergeCell ref="K13:P13"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="C3:E3"/>
@@ -1527,7 +1514,10 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="78"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="13" min="0" max="16383" man="1"/>
+  </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/apps/cards/resources/card_templates/shrm5.xlsx
+++ b/apps/cards/resources/card_templates/shrm5.xlsx
@@ -1021,19 +1021,30 @@
       <c r="D13" s="75" t="n"/>
       <c r="E13" s="76" t="n"/>
       <c r="F13" s="35" t="n"/>
-    </row>
-    <row r="14" ht="27.75" customHeight="1" s="20">
-      <c r="G14" s="22" t="n"/>
-      <c r="K14" s="64" t="inlineStr">
+      <c r="G13" s="22" t="n"/>
+      <c r="K13" s="64" t="inlineStr">
         <is>
           <t>Уважаемый пациент!</t>
         </is>
       </c>
     </row>
+    <row r="14" ht="27.75" customHeight="1" s="20">
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Перед выпиской сдайте «Индивидуальную </t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="16" t="n"/>
+      <c r="O14" s="16" t="n"/>
+      <c r="P14" s="16" t="n"/>
+    </row>
     <row r="15" ht="24.75" customHeight="1" s="20">
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перед выпиской сдайте «Индивидуальную </t>
+          <t>программу» на пост медицинской сестре.</t>
         </is>
       </c>
       <c r="K15" s="16" t="n"/>
@@ -1044,17 +1055,13 @@
       <c r="P15" s="16" t="n"/>
     </row>
     <row r="16" ht="24.75" customHeight="1" s="20">
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>программу» на пост медицинской сестре.</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
+      <c r="J16" s="49" t="n"/>
+      <c r="K16" s="49" t="n"/>
+      <c r="L16" s="49" t="n"/>
+      <c r="M16" s="49" t="n"/>
+      <c r="N16" s="49" t="n"/>
+      <c r="O16" s="49" t="n"/>
+      <c r="P16" s="49" t="n"/>
     </row>
     <row r="17" ht="1.5" customHeight="1" s="20">
       <c r="J17" s="49" t="n"/>
@@ -1483,7 +1490,6 @@
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="K14:P14"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="C7:E7"/>
@@ -1491,6 +1497,7 @@
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="A33:B33"/>
+    <mergeCell ref="K13:P13"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="C3:E3"/>
@@ -1514,9 +1521,9 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="78"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="89"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="13" min="0" max="16383" man="1"/>
+    <brk id="17" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
